--- a/repro/results/analise_extensoes/relatorio_extensoes.xlsx
+++ b/repro/results/analise_extensoes/relatorio_extensoes.xlsx
@@ -16,18 +16,20 @@
     <sheet name="P1 combinação contrastes" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="P1 dataset inteiro MAE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="P1 dataset inteiro contrastes" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="P2 checagens" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="P2 lacunas por campo" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="P2 lacunas por issue" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="P2 Jev" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="P2 MAE por versão e modelo" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="P2 fatorial MAE" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="P2 fatorial contrastes" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="P2 fatorial regressão" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="P2 lacunas x erro" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="P2 erro por campo ausente" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="P2g MAE por versão (analogia)" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="P2g contrastes (analogia)" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="P1f MAE calibração por tipo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="P1f contrastes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="P2 checagens" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="P2 lacunas por campo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="P2 lacunas por issue" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="P2 Jev" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="P2 MAE por versão e modelo" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="P2 fatorial MAE" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="P2 fatorial contrastes" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="P2 fatorial regressão" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="P2 lacunas x erro" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="P2 erro por campo ausente" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="P2g MAE por versão (analogia)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="P2g contrastes (analogia)" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,6 +518,11 @@
           <t>issues</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fora da faixa</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -538,6 +545,9 @@
       </c>
       <c r="E2" t="n">
         <v>1031</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -558,6 +568,9 @@
       <c r="E3" t="n">
         <v>503</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
@@ -577,6 +590,9 @@
       <c r="E4" t="n">
         <v>503</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -596,6 +612,9 @@
       <c r="E5" t="n">
         <v>503</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -615,6 +634,9 @@
       <c r="E6" t="n">
         <v>1031</v>
       </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -634,6 +656,9 @@
       <c r="E7" t="n">
         <v>503</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -653,6 +678,9 @@
       <c r="E8" t="n">
         <v>2078</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -666,13 +694,14 @@
           <t>within/SVR.csv</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>tamanho errado</t>
-        </is>
+      <c r="D9" t="b">
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2330</v>
+        <v>2078</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -693,6 +722,9 @@
       <c r="E10" t="n">
         <v>2078</v>
       </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -715,6 +747,9 @@
       </c>
       <c r="E11" t="n">
         <v>716</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -735,6 +770,9 @@
       <c r="E12" t="n">
         <v>284</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -754,6 +792,9 @@
       <c r="E13" t="n">
         <v>284</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -773,6 +814,9 @@
       <c r="E14" t="n">
         <v>284</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -792,6 +836,9 @@
       <c r="E15" t="n">
         <v>716</v>
       </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -811,6 +858,9 @@
       <c r="E16" t="n">
         <v>284</v>
       </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -830,6 +880,9 @@
       <c r="E17" t="n">
         <v>1437</v>
       </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -844,9 +897,12 @@
         </is>
       </c>
       <c r="D18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
+        <v>1437</v>
+      </c>
+      <c r="F18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,6 +923,9 @@
       </c>
       <c r="E19" t="n">
         <v>1437</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -884,6 +943,1361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>configuração</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MdAE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>ProjectMedian</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3.996606334841629</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>ZS1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7.303167420814479</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4.127828054298643</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3.668552036199095</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3.900452488687783</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost (texto)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.180030888696601</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.412381887435913</v>
+      </c>
+      <c r="E8" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.749579360447318</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.972275495529175</v>
+      </c>
+      <c r="E9" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.470588235294118</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3.51929737991607</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.866551518440247</v>
+      </c>
+      <c r="E11" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3.554864253393665</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>ProjectMedian</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.61731843575419</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>ZS1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6.664804469273743</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.681564245810056</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.628491620111732</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2.07122905027933</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost (texto)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.663149115093594</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.003653049468994</v>
+      </c>
+      <c r="E19" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.553436543355441</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.934131920337677</v>
+      </c>
+      <c r="E20" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1.67108938547486</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.511439949940037</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9279715418815613</v>
+      </c>
+      <c r="E22" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.605446927374302</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>716</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>contraste</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MAE A</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MAE B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Δ MAE (B − A)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IC95% inf</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>IC95% sup</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p (Wilcoxon)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p (Holm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>tipo na mediana</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ProjectMedian</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3.996606334841629</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.4106334841628959</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.667420814479638</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.1702488687782805</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0005890193270703669</v>
+      </c>
+      <c r="K2" t="n">
+        <v>884</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.004123135289492568</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>LLM: dist. por tipo × do projeto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4.127828054298643</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.668552036199095</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.4592760180995475</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.8755938914027149</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.083710407239819</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.00396748121296</v>
+      </c>
+      <c r="K3" t="n">
+        <v>884</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.02380488727776</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.127828054298643</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5418552036199095</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2827912895927602</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8167562217194568</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0001039271925614601</v>
+      </c>
+      <c r="K4" t="n">
+        <v>884</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0009353447330531405</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.668552036199095</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.08257918552036199</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.1979638009049774</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3529553167420812</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3850837522493387</v>
+      </c>
+      <c r="K5" t="n">
+        <v>884</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7701675044986773</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.900452488687783</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3144796380090498</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.08945135746606332</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7064621040723981</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.08366444217402481</v>
+      </c>
+      <c r="K6" t="n">
+        <v>884</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4183222108701241</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost (texto) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>XGBoost (texto)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.180030888696601</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5940580380178685</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3447557966734759</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8562664493547572</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.80994720219041e-11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>884</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.809947202190411e-10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.749579360447318</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1636065097685853</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.08538474067371353</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4281635838564975</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0003919915650195702</v>
+      </c>
+      <c r="K8" t="n">
+        <v>884</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.003135932520156562</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.470588235294118</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.1153846153846154</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.3308823529411765</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09220871040723962</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.09363356319641962</v>
+      </c>
+      <c r="K9" t="n">
+        <v>884</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4183222108701241</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.51929737991607</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.06667547076266275</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2071099228937836</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0769335954471141</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2374570013530297</v>
+      </c>
+      <c r="K10" t="n">
+        <v>884</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7123710040590892</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.554864253393665</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.03110859728506787</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1792986425339367</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1088871606334841</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8824667925909202</v>
+      </c>
+      <c r="K11" t="n">
+        <v>884</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8824667925909202</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>tipo na mediana</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ProjectMedian</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1.61731843575419</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.01815642458100559</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.05935754189944134</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.02583798882681564</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1478497680634144</v>
+      </c>
+      <c r="K12" t="n">
+        <v>716</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7392488403170718</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>LLM: dist. por tipo × do projeto</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1.681564245810056</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.628491620111732</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.05307262569832402</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.11875</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01675977653631285</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1211923456636531</v>
+      </c>
+      <c r="K13" t="n">
+        <v>716</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7271540739819184</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.681564245810056</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0824022346368715</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01256983240223464</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1536312849162011</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.007113810551882393</v>
+      </c>
+      <c r="K14" t="n">
+        <v>716</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.05691048441505914</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.628491620111732</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.02932960893854749</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.04399441340782123</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.09986033519553073</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1489722858537362</v>
+      </c>
+      <c r="K15" t="n">
+        <v>716</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7392488403170718</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.07122905027933</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4720670391061452</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2401885474860335</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6864525139664804</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9.644777585034093e-12</v>
+      </c>
+      <c r="K16" t="n">
+        <v>716</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.644777585034092e-11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost (texto) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>XGBoost (texto)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.663149115093594</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.06398710392040914</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2308945169870081</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2944828639524941</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.004060825233422018</v>
+      </c>
+      <c r="K17" t="n">
+        <v>716</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.03654742710079817</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.553436543355441</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.0457254678177434</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.3088484352194397</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1397534304366098</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1886294022110985</v>
+      </c>
+      <c r="K18" t="n">
+        <v>716</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.7392488403170718</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.67108938547486</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.07192737430167598</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.05028805865921788</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1854137569832401</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.009737844673201594</v>
+      </c>
+      <c r="K19" t="n">
+        <v>716</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.06816491271241115</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.511439949940037</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.08772206123314756</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2251296382168485</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0155138952480681</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8771992486932699</v>
+      </c>
+      <c r="K20" t="n">
+        <v>716</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8771992486932699</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.605446927374302</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.006284916201117319</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.03002793296089385</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.04259776536312849</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.286891627053746</v>
+      </c>
+      <c r="K21" t="n">
+        <v>716</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.7392488403170718</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:A21"/>
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -957,7 +2371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1111,7 +2525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1234,7 +2648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3058,7 +4472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3346,1582 +4760,6 @@
   <mergeCells count="2">
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="A2:A6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>versao</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sem cartão</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>com cartão</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Δ do cartão</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>agile_limpo</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9.456</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.987</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>parafrasear</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>11.481</v>
-      </c>
-      <c r="D3" t="n">
-        <v>10.532</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.949</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>melhorar</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>11.646</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10.342</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1.304</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>11.544</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.734</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10.544</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.101</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>neo_limpo</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.057</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>parafrasear</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6.981</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.189</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.792</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>melhorar</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7.604</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.264</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="D10" t="n">
-        <v>7.132</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>6.623</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.396</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.226</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A2:A6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>contraste</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MAE A</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MAE B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Δ MAE (B − A)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>IC95% inf</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>IC95% sup</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>p (Wilcoxon)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>p (Holm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>agile_limpo</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>só o contexto no estimador</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>original + cartão</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9.456</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.987</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.392</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="K2" t="n">
-        <v>79</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>só mexer no texto (controle)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>parafrasear</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F3" t="n">
-        <v>11.481</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.659</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K3" t="n">
-        <v>79</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.033</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>reescrita livre, sem contexto</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>melhorar</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11.646</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.203</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.873</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K4" t="n">
-        <v>79</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>reescrita livre com contexto</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F5" t="n">
-        <v>11.544</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.101</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.747</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="K5" t="n">
-        <v>79</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.032</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>reescrita estruturada com contexto</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.658</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="K6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>estruturada × livre (mesma informação)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>11.544</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.101</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.861</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.316</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>79</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.052</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>estruturada × livre, com cartão no estimador</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>melhorar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10.544</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.266</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.924</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="K8" t="n">
-        <v>79</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.847</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>estruturada, com cartão no estimador</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>original + cartão</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>9.456</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10.544</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.734</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K9" t="n">
-        <v>79</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>tudo junto (livre)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>melhorar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.342</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="K10" t="n">
-        <v>79</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.847</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>tudo junto (estruturada)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>10.443</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10.544</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.544</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="K11" t="n">
-        <v>79</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>neo_limpo</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>só o contexto no estimador</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>original + cartão</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.057</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-1.774</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.321</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K12" t="n">
-        <v>53</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>só mexer no texto (controle)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>parafrasear</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6.981</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.434</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="K13" t="n">
-        <v>53</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.166</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>reescrita livre, sem contexto</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>melhorar</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F14" t="n">
-        <v>7.604</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.377</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.132</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K14" t="n">
-        <v>53</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>reescrita livre com contexto</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.509</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K15" t="n">
-        <v>53</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.021</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>reescrita estruturada com contexto</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F16" t="n">
-        <v>6.623</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5659999999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="K16" t="n">
-        <v>53</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.895</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>estruturada × livre (mesma informação)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.623</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-2.113</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.226</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="K17" t="n">
-        <v>53</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.099</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>estruturada × livre, com cartão no estimador</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>melhorar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>7.132</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6.396</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.736</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-1.585</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="K18" t="n">
-        <v>53</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.341</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>estruturada, com cartão no estimador</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>original + cartão</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6.396</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.226</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="K19" t="n">
-        <v>53</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>tudo junto (livre)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>melhorar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7.132</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.038</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="K20" t="n">
-        <v>53</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.225</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>tudo junto (estruturada)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6.226</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6.396</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.774</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.094</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="K21" t="n">
-        <v>53</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.895</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>ambos</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>só o contexto no estimador</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>original + cartão</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F22" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-1.015</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.5610000000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>132</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>só mexer no texto (controle)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>parafrasear</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F23" t="n">
-        <v>9.673999999999999</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.386</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>132</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>reescrita livre, sem contexto</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>melhorar</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.023</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.273</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.788</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>132</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>reescrita livre com contexto</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F25" t="n">
-        <v>10.038</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.288</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.841</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>132</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>reescrita estruturada com contexto</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8.909000000000001</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.387</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="K26" t="n">
-        <v>132</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>estruturada × livre (mesma informação)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>10.038</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8.909000000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-1.129</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-0.523</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>132</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>estruturada × livre, com cartão no estimador</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>melhorar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8.879</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.455</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-0.985</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="K28" t="n">
-        <v>132</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.177</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>estruturada, com cartão no estimador</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>original + cartão</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>7.735</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8.879</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.144</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>132</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>tudo junto (livre)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>melhorar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.182</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K30" t="n">
-        <v>132</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.119</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>tudo junto (estruturada)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>estruturar_contexto + cartão</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8.879</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-0.402</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="K31" t="n">
-        <v>132</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="A2:A11"/>
-    <mergeCell ref="A22:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4933,7 +4771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4944,32 +4782,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>termo</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>coef. (SP)</t>
+          <t>sem cartão</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>IC95% inf</t>
+          <t>com cartão</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>IC95% sup</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n issues</t>
+          <t>Δ do cartão</t>
         </is>
       </c>
     </row>
@@ -4981,424 +4809,180 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>texto estruturar_contexto</t>
+          <t>original</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>10.443</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.707</v>
+        <v>9.456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>79</v>
+        <v>-0.987</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>texto melhorar</t>
+          <t>parafrasear</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.203</v>
+        <v>11.481</v>
       </c>
       <c r="D3" t="n">
-        <v>0.49</v>
+        <v>10.532</v>
       </c>
       <c r="E3" t="n">
-        <v>1.915</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>79</v>
+        <v>-0.949</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>texto melhorar_contexto</t>
+          <t>melhorar</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.101</v>
+        <v>11.646</v>
       </c>
       <c r="D4" t="n">
-        <v>0.411</v>
+        <v>10.342</v>
       </c>
       <c r="E4" t="n">
-        <v>1.791</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G4" t="n">
-        <v>79</v>
+        <v>-1.304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>texto parafrasear</t>
+          <t>melhorar_contexto</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.038</v>
+        <v>11.544</v>
       </c>
       <c r="D5" t="n">
-        <v>0.382</v>
+        <v>10.81</v>
       </c>
       <c r="E5" t="n">
-        <v>1.694</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G5" t="n">
-        <v>79</v>
+        <v>-0.734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>cartão</t>
+          <t>estruturar_contexto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.987</v>
+        <v>10.443</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.611</v>
+        <v>10.544</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.364</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G6" t="n">
-        <v>79</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>texto estruturar_contexto × cartão</t>
+          <t>original</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.089</v>
+        <v>6.226</v>
       </c>
       <c r="D7" t="n">
-        <v>0.247</v>
+        <v>5.17</v>
       </c>
       <c r="E7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G7" t="n">
-        <v>79</v>
+        <v>-1.057</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>texto melhorar × cartão</t>
+          <t>parafrasear</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.316</v>
+        <v>6.981</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.015</v>
+        <v>6.189</v>
       </c>
       <c r="E8" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="G8" t="n">
-        <v>79</v>
+        <v>-0.792</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>texto melhorar_contexto × cartão</t>
+          <t>melhorar</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.253</v>
+        <v>7.604</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.429</v>
+        <v>6.264</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="G9" t="n">
-        <v>79</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>texto parafrasear × cartão</t>
+          <t>melhorar_contexto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.038</v>
+        <v>7.792</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.715</v>
+        <v>7.132</v>
       </c>
       <c r="E10" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="G10" t="n">
-        <v>79</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>neo_limpo</t>
-        </is>
-      </c>
+      <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>texto estruturar_contexto</t>
+          <t>estruturar_contexto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.396</v>
+        <v>6.623</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.648</v>
+        <v>6.396</v>
       </c>
       <c r="E11" t="n">
-        <v>1.441</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="G11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>texto melhorar</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1.377</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.205</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>texto melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.582</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="G13" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>texto parafrasear</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="G14" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>cartão</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.057</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1.851</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.262</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>texto estruturar_contexto × cartão</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.269</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="G16" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>texto melhorar × cartão</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.283</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-1.225</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="G17" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>texto melhorar_contexto × cartão</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.599</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.391</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="G18" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>texto parafrasear × cartão</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.759</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.287</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="G19" t="n">
-        <v>53</v>
+        <v>-0.226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5410,7 +4994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5421,22 +5005,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n_lacunas ×</t>
+          <t>contraste</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rho (Spearman)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MAE A</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MAE B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Δ MAE (B − A)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IC95% inf</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>IC95% sup</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p (Wilcoxon)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>n</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p (Holm)</t>
         </is>
       </c>
     </row>
@@ -5448,214 +5067,1275 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SP real</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.113</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.323</v>
+          <t>só o contexto no estimador</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>original + cartão</t>
+        </is>
       </c>
       <c r="E2" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.392</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="K2" t="n">
         <v>79</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>|erro| KNN (texto original)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.026</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.823</v>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>parafrasear</t>
+        </is>
       </c>
       <c r="E3" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.481</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K3" t="n">
         <v>79</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.033</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>|erro| LLM:llama3 (texto original)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.233</v>
+          <t>reescrita livre, sem contexto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
       </c>
       <c r="E4" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.646</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.873</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K4" t="n">
         <v>79</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>|erro| LLM:llama3 + cartão (texto original)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.646</v>
+          <t>reescrita livre com contexto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
       </c>
       <c r="E5" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.544</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K5" t="n">
         <v>79</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>|erro| ProjectMedian (texto original)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.066</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5610000000000001</v>
+          <t>reescrita estruturada com contexto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
       </c>
       <c r="E6" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="K6" t="n">
         <v>79</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>|erro| XGBoost (texto original)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.997</v>
+          <t>estruturada × livre (mesma informação)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
       </c>
       <c r="E7" t="n">
+        <v>11.544</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.101</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.861</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K7" t="n">
         <v>79</v>
       </c>
+      <c r="L7" t="n">
+        <v>0.052</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>neo_limpo</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>SP real</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.274</v>
+          <t>estruturada × livre, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>melhorar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>10.81</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.544</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.924</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K8" t="n">
+        <v>79</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>|erro| KNN (texto original)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.618</v>
+          <t>estruturada, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>original + cartão</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>9.456</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.544</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.734</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K9" t="n">
+        <v>79</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>|erro| LLM:llama3 (texto original)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.066</v>
+          <t>tudo junto (livre)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>melhorar_contexto + cartão</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>10.443</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.342</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="K10" t="n">
+        <v>79</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>|erro| LLM:llama3 + cartão (texto original)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.05</v>
+          <t>tudo junto (estruturada)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
       </c>
       <c r="E11" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.544</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K11" t="n">
+        <v>79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>só o contexto no estimador</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>original + cartão</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.057</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.774</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.321</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K12" t="n">
         <v>53</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>|erro| ProjectMedian (texto original)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E12" t="n">
-        <v>53</v>
+      <c r="L12" t="n">
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>|erro| XGBoost (texto original)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.38</v>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>parafrasear</t>
+        </is>
       </c>
       <c r="E13" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.981</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K13" t="n">
         <v>53</v>
       </c>
+      <c r="L13" t="n">
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre, sem contexto</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.604</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>53</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre com contexto</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K15" t="n">
+        <v>53</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>reescrita estruturada com contexto</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.623</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5659999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="K16" t="n">
+        <v>53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre (mesma informação)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.623</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2.113</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K17" t="n">
+        <v>53</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>melhorar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7.132</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.396</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.736</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.585</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="K18" t="n">
+        <v>53</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.341</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>estruturada, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>original + cartão</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.396</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K19" t="n">
+        <v>53</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (livre)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>melhorar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.132</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="K20" t="n">
+        <v>53</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (estruturada)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6.226</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.396</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="K21" t="n">
+        <v>53</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>só o contexto no estimador</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>original + cartão</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.5610000000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>132</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>parafrasear</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.673999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>132</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre, sem contexto</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.023</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>132</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre com contexto</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.038</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>132</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>reescrita estruturada com contexto</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8.909000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K26" t="n">
+        <v>132</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre (mesma informação)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>10.038</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.909000000000001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.129</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.523</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>132</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>melhorar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.879</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.455</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.985</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="K28" t="n">
+        <v>132</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>estruturada, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>original + cartão</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>7.735</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.879</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>132</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (livre)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>melhorar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K30" t="n">
+        <v>132</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.119</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (estruturada)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>estruturar_contexto + cartão</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.879</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="K31" t="n">
+        <v>132</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A2:A7"/>
+  <mergeCells count="3">
+    <mergeCell ref="A12:A21"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A22:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5667,7 +6347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5678,32 +6358,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>termo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MAE LLM com o campo</t>
+          <t>coef. (SP)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MAE LLM sem o campo</t>
+          <t>IC95% inf</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>n com</t>
+          <t>IC95% sup</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>n sem</t>
+          <t>p</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p (Mann-Whitney)</t>
+          <t>n issues</t>
         </is>
       </c>
     </row>
@@ -5715,78 +6395,424 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Affected components</t>
+          <t>texto estruturar_contexto</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.729</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>8.222</v>
+        <v>-0.707</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>0.707</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.149</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Acceptance criteria</t>
+          <t>texto melhorar</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.143</v>
+        <v>1.203</v>
       </c>
       <c r="D3" t="n">
-        <v>10.958</v>
+        <v>0.49</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>1.915</v>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>0.001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.417</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G4" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>texto parafrasear</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G5" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>cartão</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.611</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.364</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G6" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>texto estruturar_contexto × cartão</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G7" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar × cartão</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G8" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar_contexto × cartão</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="G9" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>texto parafrasear × cartão</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.715</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="G10" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>neo_limpo</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Acceptance criteria</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>4.417</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.756</v>
-      </c>
-      <c r="E4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.111</v>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>texto estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.648</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="G11" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G13" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>texto parafrasear</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="G14" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>cartão</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.057</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.851</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.262</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>texto estruturar_contexto × cartão</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.269</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="G16" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar × cartão</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.283</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.225</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G17" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>texto melhorar_contexto × cartão</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.599</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="G18" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>texto parafrasear × cartão</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.759</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="G19" t="n">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5798,7 +6824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5824,7 +6850,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sem número</t>
+          <t>inválidas (sem número ou fora da faixa)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -5981,61 +7007,61 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.770471064755267</v>
+        <v>3.362240668790761</v>
       </c>
       <c r="D9" t="n">
-        <v>2.168387413024902</v>
+        <v>1.822869716486008</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>503</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.770471064755267</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.168387413024902</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>neo_limpo</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>ZS1</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>6.482394366197183</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>ZS1 + cartão</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5.595070422535211</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>284</v>
@@ -6045,11 +7071,11 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + placebo</t>
+          <t>ZS1 + cartão</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.661971830985915</v>
+        <v>5.595070422535211</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -6065,14 +7091,14 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, sorteados</t>
+          <t>ZS1 + placebo</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.880281690140845</v>
+        <v>5.661971830985915</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -6085,11 +7111,11 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, parecidos</t>
+          <t>FS mesmo projeto, sorteados</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.626760563380282</v>
+        <v>2.880281690140845</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -6105,11 +7131,11 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>FS parecidos + cartão</t>
+          <t>FS mesmo projeto, parecidos</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.637323943661972</v>
+        <v>2.626760563380282</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -6125,17 +7151,17 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>ProjectMedian</t>
+          <t>FS parecidos + cartão</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.908450704225352</v>
+        <v>2.623239436619718</v>
       </c>
       <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>284</v>
@@ -6145,14 +7171,14 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ProjectMedian</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.092353780504683</v>
+        <v>1.908450704225352</v>
       </c>
       <c r="D17" t="n">
-        <v>1.126487374305725</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -6161,10 +7187,50 @@
         <v>284</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.819223232725218</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.011535713656055</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.092353780504683</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.126487374305725</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>284</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6176,118 +7242,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>agile_limpo</t>
+          <t>n_lacunas ×</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>neo_limpo</t>
+          <t>rho (Spearman)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6.127</v>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SP real</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>3.698</v>
+        <v>-0.113</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="E2" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>parafrasear</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>11.911</v>
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>|erro| KNN (texto original)</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>2.811</v>
+        <v>-0.026</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="E3" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>melhorar</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>8.038</v>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>|erro| LLM:llama3 (texto original)</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>3.321</v>
+        <v>0.136</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="E4" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>melhorar_contexto</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7.418</v>
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>|erro| LLM:llama3 + cartão (texto original)</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>3.396</v>
+        <v>0.052</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="E5" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>estruturar_contexto</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6.785</v>
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>|erro| ProjectMedian (texto original)</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>3.566</v>
+        <v>-0.066</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>(ref.) mediana do projeto</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7.367</v>
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>|erro| XGBoost (texto original)</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>3.434</v>
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E7" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>(ref.) ZS1, texto original</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>10.443</v>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>SP real</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>6.226</v>
+        <v>0.153</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>|erro| KNN (texto original)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>|erro| LLM:llama3 (texto original)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>|erro| LLM:llama3 + cartão (texto original)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>|erro| ProjectMedian (texto original)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>|erro| XGBoost (texto original)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6298,6 +7499,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MAE LLM com o campo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MAE LLM sem o campo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n com</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n sem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>p (Mann-Whitney)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Affected components</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10.729</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.222</v>
+      </c>
+      <c r="E2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance criteria</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5.143</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.958</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance criteria</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.756</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6.127</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.698</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>parafrasear</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8.063000000000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.811</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8.038</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.321</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7.418</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.396</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.566</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>(ref.) mediana do projeto</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7.367</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.434</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>(ref.) ZS1, texto original</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10.443</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.226</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -6388,16 +7842,16 @@
         <v>6.127</v>
       </c>
       <c r="F2" t="n">
-        <v>11.911</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>5.785</v>
+        <v>1.937</v>
       </c>
       <c r="H2" t="n">
         <v>-0.026</v>
       </c>
       <c r="I2" t="n">
-        <v>16.595</v>
+        <v>4.95</v>
       </c>
       <c r="J2" t="n">
         <v>0.478</v>
@@ -6469,22 +7923,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.911</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>8.038</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.873</v>
+        <v>-0.025</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.089</v>
+        <v>-0.747</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="J4" t="n">
-        <v>0.959</v>
+        <v>0.892</v>
       </c>
       <c r="K4" t="n">
         <v>79</v>
@@ -6553,22 +8007,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11.911</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>7.418</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.494</v>
+        <v>-0.646</v>
       </c>
       <c r="H6" t="n">
-        <v>-13.519</v>
+        <v>-2.038</v>
       </c>
       <c r="I6" t="n">
-        <v>0.418</v>
+        <v>0.582</v>
       </c>
       <c r="J6" t="n">
-        <v>0.738</v>
+        <v>0.756</v>
       </c>
       <c r="K6" t="n">
         <v>79</v>
@@ -6637,22 +8091,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11.911</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>6.785</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.127</v>
+        <v>-1.278</v>
       </c>
       <c r="H8" t="n">
-        <v>-14.342</v>
+        <v>-3.545</v>
       </c>
       <c r="I8" t="n">
-        <v>0.152</v>
+        <v>0.418</v>
       </c>
       <c r="J8" t="n">
-        <v>0.416</v>
+        <v>0.446</v>
       </c>
       <c r="K8" t="n">
         <v>79</v>
@@ -6984,16 +8438,16 @@
         <v>5.152</v>
       </c>
       <c r="F16" t="n">
-        <v>8.257999999999999</v>
+        <v>5.955</v>
       </c>
       <c r="G16" t="n">
-        <v>3.106</v>
+        <v>0.803</v>
       </c>
       <c r="H16" t="n">
         <v>-0.432</v>
       </c>
       <c r="I16" t="n">
-        <v>9.515000000000001</v>
+        <v>2.591</v>
       </c>
       <c r="J16" t="n">
         <v>0.416</v>
@@ -7065,22 +8519,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.257999999999999</v>
+        <v>5.955</v>
       </c>
       <c r="F18" t="n">
         <v>6.144</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.114</v>
+        <v>0.189</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.091</v>
+        <v>-0.356</v>
       </c>
       <c r="I18" t="n">
-        <v>0.636</v>
+        <v>0.735</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.513</v>
       </c>
       <c r="K18" t="n">
         <v>132</v>
@@ -7149,22 +8603,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.257999999999999</v>
+        <v>5.955</v>
       </c>
       <c r="F20" t="n">
         <v>5.803</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.455</v>
+        <v>-0.152</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.72</v>
+        <v>-1.038</v>
       </c>
       <c r="I20" t="n">
-        <v>0.508</v>
+        <v>0.614</v>
       </c>
       <c r="J20" t="n">
-        <v>0.519</v>
+        <v>0.512</v>
       </c>
       <c r="K20" t="n">
         <v>132</v>
@@ -7233,22 +8687,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.257999999999999</v>
+        <v>5.955</v>
       </c>
       <c r="F22" t="n">
         <v>5.492</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.765</v>
+        <v>-0.462</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.151999999999999</v>
+        <v>-1.849</v>
       </c>
       <c r="I22" t="n">
-        <v>0.44</v>
+        <v>0.637</v>
       </c>
       <c r="J22" t="n">
-        <v>0.646</v>
+        <v>0.612</v>
       </c>
       <c r="K22" t="n">
         <v>132</v>
@@ -8047,22 +9501,22 @@
         <v>2.626760563380282</v>
       </c>
       <c r="F17" t="n">
-        <v>2.637323943661972</v>
+        <v>2.623239436619718</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01056338028169014</v>
+        <v>-0.00352112676056338</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1373239436619718</v>
+        <v>-0.1549295774647887</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1620598591549283</v>
+        <v>0.1549295774647887</v>
       </c>
       <c r="J17" t="n">
-        <v>0.775677958906007</v>
+        <v>0.9156539447634165</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002792191746973067</v>
+        <v>-0.00914257474672597</v>
       </c>
       <c r="L17" t="n">
         <v>284</v>
@@ -8092,28 +9546,28 @@
         <v>5.595070422535211</v>
       </c>
       <c r="F18" t="n">
-        <v>2.637323943661972</v>
+        <v>2.623239436619718</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.957746478873239</v>
+        <v>-2.971830985915493</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.397887323943662</v>
+        <v>-3.411971830985915</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.51056338028169</v>
+        <v>-2.528169014084507</v>
       </c>
       <c r="J18" t="n">
-        <v>3.722674020166573e-29</v>
+        <v>3.157448862333101e-29</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7868297504324191</v>
+        <v>-0.787521620953793</v>
       </c>
       <c r="L18" t="n">
         <v>284</v>
       </c>
       <c r="M18" t="n">
-        <v>2.978139216133258e-28</v>
+        <v>2.525959089866481e-28</v>
       </c>
     </row>
     <row r="19">
@@ -8203,7 +9657,7 @@
         <v>284</v>
       </c>
       <c r="M20" t="n">
-        <v>1.598946639082231e-05</v>
+        <v>1.998683298852789e-05</v>
       </c>
     </row>
     <row r="21">
@@ -8227,28 +9681,28 @@
         <v>1.908450704225352</v>
       </c>
       <c r="F21" t="n">
-        <v>2.637323943661972</v>
+        <v>2.623239436619718</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7288732394366197</v>
+        <v>0.7147887323943662</v>
       </c>
       <c r="H21" t="n">
-        <v>0.352112676056338</v>
+        <v>0.3380281690140845</v>
       </c>
       <c r="I21" t="n">
-        <v>1.147887323943662</v>
+        <v>1.133802816901408</v>
       </c>
       <c r="J21" t="n">
-        <v>2.880351777234495e-06</v>
+        <v>4.094269329087371e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3234741784037559</v>
+        <v>0.3188040523844823</v>
       </c>
       <c r="L21" t="n">
         <v>284</v>
       </c>
       <c r="M21" t="n">
-        <v>1.440175888617247e-05</v>
+        <v>1.998683298852789e-05</v>
       </c>
     </row>
   </sheetData>
@@ -8266,7 +9720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8317,10 +9771,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -8359,9 +9818,12 @@
         <v>2.68</v>
       </c>
       <c r="J2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.8</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -8394,9 +9856,12 @@
         <v>1.36</v>
       </c>
       <c r="J3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K3" t="n">
         <v>2.05</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>33</v>
       </c>
     </row>
@@ -8429,9 +9894,12 @@
         <v>13.37</v>
       </c>
       <c r="J4" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="K4" t="n">
         <v>13.22</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>59</v>
       </c>
     </row>
@@ -8464,9 +9932,12 @@
         <v>1.44</v>
       </c>
       <c r="J5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.58</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>77</v>
       </c>
     </row>
@@ -8499,9 +9970,12 @@
         <v>2.49</v>
       </c>
       <c r="J6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.48</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>43</v>
       </c>
     </row>
@@ -8534,9 +10008,12 @@
         <v>2.88</v>
       </c>
       <c r="J7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K7" t="n">
         <v>2.99</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>104</v>
       </c>
     </row>
@@ -8569,9 +10046,12 @@
         <v>0.67</v>
       </c>
       <c r="J8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.29</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -8604,9 +10084,12 @@
         <v>1.82</v>
       </c>
       <c r="J9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.12</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>150</v>
       </c>
     </row>
@@ -8643,9 +10126,12 @@
         <v>1.23</v>
       </c>
       <c r="J10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K10" t="n">
         <v>1.26</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>22</v>
       </c>
     </row>
@@ -8678,9 +10164,12 @@
         <v>2.51</v>
       </c>
       <c r="J11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.62</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>45</v>
       </c>
     </row>
@@ -8713,9 +10202,12 @@
         <v>1.85</v>
       </c>
       <c r="J12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K12" t="n">
         <v>1.78</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -8742,15 +10234,18 @@
         <v>1.73</v>
       </c>
       <c r="H13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
       </c>
       <c r="J13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K13" t="n">
         <v>1.21</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>91</v>
       </c>
     </row>
@@ -8783,9 +10278,12 @@
         <v>2.17</v>
       </c>
       <c r="J14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.41</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8818,9 +10316,12 @@
         <v>8.109999999999999</v>
       </c>
       <c r="J15" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K15" t="n">
         <v>6.83</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8853,9 +10354,12 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.36</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>13</v>
       </c>
     </row>
@@ -8888,9 +10392,12 @@
         <v>4.17</v>
       </c>
       <c r="J17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.92</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8923,9 +10430,12 @@
         <v>2.58</v>
       </c>
       <c r="J18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K18" t="n">
         <v>5.48</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8944,7 +10454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9105,14 +10615,14 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>MAE FS mesmo projeto, parecidos</t>
+          <t>MAE SVR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.157057654075547</v>
+        <v>3.362240668790761</v>
       </c>
       <c r="D7" t="n">
-        <v>8.831439393939394</v>
+        <v>3.950983338596297</v>
       </c>
       <c r="E7" t="n">
         <v>503</v>
@@ -9121,48 +10631,48 @@
         <v>528</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005084551827116122</v>
+        <v>0.0114453292218759</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>MAE FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.157057654075547</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.287878787878788</v>
+      </c>
+      <c r="E8" t="n">
+        <v>503</v>
+      </c>
+      <c r="F8" t="n">
+        <v>528</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0005198579958518247</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>neo_limpo</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>SP real (média)</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>3.390845070422535</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>2.858796296296296</v>
-      </c>
-      <c r="E8" t="n">
-        <v>284</v>
-      </c>
-      <c r="F8" t="n">
-        <v>432</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.02245878595558264</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>projetos</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19</v>
       </c>
       <c r="E9" t="n">
         <v>284</v>
@@ -9170,20 +10680,22 @@
       <c r="F9" t="n">
         <v>432</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0.02245878595558264</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>MAE ZS1</t>
+          <t>projetos</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.482394366197183</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>6.784722222222222</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>284</v>
@@ -9191,22 +10703,20 @@
       <c r="F10" t="n">
         <v>432</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.5292938953262095</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>MAE ProjectMedian</t>
+          <t>MAE ZS1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.908450704225352</v>
+        <v>6.482394366197183</v>
       </c>
       <c r="D11" t="n">
-        <v>1.425925925925926</v>
+        <v>6.784722222222222</v>
       </c>
       <c r="E11" t="n">
         <v>284</v>
@@ -9215,21 +10725,21 @@
         <v>432</v>
       </c>
       <c r="G11" t="n">
-        <v>5.09115538753534e-05</v>
+        <v>0.5292938953262095</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>MAE XGBoost</t>
+          <t>MAE ProjectMedian</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.092353780504683</v>
+        <v>1.908450704225352</v>
       </c>
       <c r="D12" t="n">
-        <v>1.380986788758525</v>
+        <v>1.425925925925926</v>
       </c>
       <c r="E12" t="n">
         <v>284</v>
@@ -9238,21 +10748,21 @@
         <v>432</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000633202846572994</v>
+        <v>5.09115538753534e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>MAE FS mesmo projeto, parecidos</t>
+          <t>MAE XGBoost</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.626760563380282</v>
+        <v>2.092353780504683</v>
       </c>
       <c r="D13" t="n">
-        <v>1.706018518518519</v>
+        <v>1.380986788758525</v>
       </c>
       <c r="E13" t="n">
         <v>284</v>
@@ -9261,13 +10771,59 @@
         <v>432</v>
       </c>
       <c r="G13" t="n">
+        <v>0.000633202846572994</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>MAE SVR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.819223232725218</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.458732290815749</v>
+      </c>
+      <c r="E14" t="n">
+        <v>284</v>
+      </c>
+      <c r="F14" t="n">
+        <v>432</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.007648357093594514</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>MAE FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2.626760563380282</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.706018518518519</v>
+      </c>
+      <c r="E15" t="n">
+        <v>284</v>
+      </c>
+      <c r="F15" t="n">
+        <v>432</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.576426649444063e-07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A2:A8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9495,7 +11051,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.033450704225352</v>
+        <v>2.026408450704225</v>
       </c>
       <c r="D12" t="n">
         <v>1.5</v>
@@ -9900,19 +11456,19 @@
         <v>1.908450704225352</v>
       </c>
       <c r="E10" t="n">
-        <v>2.033450704225352</v>
+        <v>2.026408450704225</v>
       </c>
       <c r="F10" t="n">
-        <v>0.125</v>
+        <v>0.1179577464788732</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0897887323943662</v>
+        <v>-0.09683098591549295</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3573943661971831</v>
+        <v>0.3503521126760563</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0647335437368923</v>
+        <v>0.07729173015163272</v>
       </c>
       <c r="J10" t="n">
         <v>284</v>
@@ -9930,28 +11486,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.637323943661972</v>
+        <v>2.623239436619718</v>
       </c>
       <c r="E11" t="n">
-        <v>2.033450704225352</v>
+        <v>2.026408450704225</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6038732394366197</v>
+        <v>-0.596830985915493</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.823943661971831</v>
+        <v>-0.8151408450704225</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4014084507042254</v>
+        <v>-0.3943661971830986</v>
       </c>
       <c r="I11" t="n">
-        <v>2.250707880868414e-11</v>
+        <v>3.390333772675758e-11</v>
       </c>
       <c r="J11" t="n">
         <v>284</v>
       </c>
       <c r="K11" t="n">
-        <v>1.350424728521048e-10</v>
+        <v>2.034200263605455e-10</v>
       </c>
     </row>
     <row r="12">
@@ -10045,7 +11601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10112,7 +11668,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.063045586808923</v>
+        <v>3.736178467507274</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -10168,14 +11724,14 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>média(mediana do projeto, FS parecidos)</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.581474296799224</v>
+        <v>3.663750008904556</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>2.028609764991654</v>
       </c>
       <c r="E6" t="n">
         <v>1031</v>
@@ -10185,41 +11741,41 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>média(mediana do projeto, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3.470417070805043</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1031</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>neo_limpo</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>ZS1</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C8" t="n">
         <v>6.664804469273743</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>6</v>
-      </c>
-      <c r="E7" t="n">
-        <v>716</v>
-      </c>
-      <c r="F7" t="n">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>FS mesmo projeto, parecidos</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2.07122905027933</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>716</v>
@@ -10232,11 +11788,11 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>ProjectMedian</t>
+          <t>FS mesmo projeto, parecidos</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.61731843575419</v>
+        <v>2.07122905027933</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -10252,14 +11808,14 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ProjectMedian</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.663149115093594</v>
+        <v>1.61731843575419</v>
       </c>
       <c r="D10" t="n">
-        <v>1.003653049468994</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>716</v>
@@ -10272,14 +11828,14 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>média(mediana do projeto, FS parecidos)</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.67108938547486</v>
+        <v>1.663149115093594</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.003653049468994</v>
       </c>
       <c r="E11" t="n">
         <v>716</v>
@@ -10288,10 +11844,50 @@
         <v>716</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.601720318053583</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9004870910512414</v>
+      </c>
+      <c r="E12" t="n">
+        <v>716</v>
+      </c>
+      <c r="F12" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>média(mediana do projeto, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.67108938547486</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>716</v>
+      </c>
+      <c r="F13" t="n">
+        <v>716</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10383,25 +11979,25 @@
         <v>7.226964112512124</v>
       </c>
       <c r="E2" t="n">
-        <v>6.063045586808923</v>
+        <v>3.736178467507274</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.163918525703201</v>
+        <v>-3.49078564500485</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.669277400581959</v>
+        <v>-3.870053346265761</v>
       </c>
       <c r="H2" t="n">
-        <v>3.272575169738118</v>
+        <v>-3.115349175557712</v>
       </c>
       <c r="I2" t="n">
-        <v>1.008724840416207e-79</v>
+        <v>1.211918977488495e-80</v>
       </c>
       <c r="J2" t="n">
         <v>1031</v>
       </c>
       <c r="K2" t="n">
-        <v>4.034899361664829e-79</v>
+        <v>4.847675909953979e-80</v>
       </c>
     </row>
     <row r="3">
@@ -10420,25 +12016,25 @@
         <v>3.798254122211445</v>
       </c>
       <c r="E3" t="n">
-        <v>6.063045586808923</v>
+        <v>3.736178467507274</v>
       </c>
       <c r="F3" t="n">
-        <v>2.264791464597478</v>
+        <v>-0.06207565470417071</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1901309408341416</v>
+        <v>-0.4034917555771096</v>
       </c>
       <c r="H3" t="n">
-        <v>6.615058195926284</v>
+        <v>0.2628516003879728</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9558617782414857</v>
+        <v>0.9409735632839344</v>
       </c>
       <c r="J3" t="n">
         <v>1031</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9558617782414857</v>
+        <v>0.9409735632839344</v>
       </c>
     </row>
     <row r="4">
@@ -10453,25 +12049,25 @@
         <v>3.798254122211445</v>
       </c>
       <c r="E4" t="n">
-        <v>4.581474296799224</v>
+        <v>3.470417070805043</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7832201745877788</v>
+        <v>-0.3278370514064016</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4039767216294859</v>
+        <v>-0.518913676042677</v>
       </c>
       <c r="H4" t="n">
-        <v>2.869604752667312</v>
+        <v>-0.1445077594568382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001231562267746445</v>
+        <v>0.0007433466316552775</v>
       </c>
       <c r="J4" t="n">
         <v>1031</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003694686803239334</v>
+        <v>0.002230039894965833</v>
       </c>
     </row>
     <row r="5">
@@ -10487,28 +12083,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.063045586808923</v>
+        <v>3.736178467507274</v>
       </c>
       <c r="E5" t="n">
-        <v>4.581474296799224</v>
+        <v>3.470417070805043</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.481571290009699</v>
+        <v>-0.2657613967022309</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.773181377303588</v>
+        <v>-0.4830383123181377</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1774975751697381</v>
+        <v>-0.05333414161008747</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004830171162686751</v>
+        <v>0.006900937801595388</v>
       </c>
       <c r="J5" t="n">
         <v>1031</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009660342325373501</v>
+        <v>0.01380187560319078</v>
       </c>
     </row>
     <row r="6">

--- a/repro/results/analise_extensoes/relatorio_extensoes.xlsx
+++ b/repro/results/analise_extensoes/relatorio_extensoes.xlsx
@@ -30,6 +30,9 @@
     <sheet name="P2 erro por campo ausente" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="P2g MAE por versão (analogia)" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="P2g contrastes (analogia)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="P2h fidelidade por versão" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="P2h exemplos de reescritas susp" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="P2h sensibilidade" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -943,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,14 +1120,14 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, FS parecidos)</t>
+          <t>SVR (texto)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.470588235294118</v>
+        <v>3.806327292442361</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>2.000420120508622</v>
       </c>
       <c r="E10" t="n">
         <v>884</v>
@@ -1134,14 +1137,14 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, XGBoost texto+meta)</t>
+          <t>SVR texto+meta</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.51929737991607</v>
+        <v>3.309497062222206</v>
       </c>
       <c r="D11" t="n">
-        <v>1.866551518440247</v>
+        <v>1.631061044767066</v>
       </c>
       <c r="E11" t="n">
         <v>884</v>
@@ -1151,11 +1154,11 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+          <t>média(PM×tipo, FS parecidos)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.554864253393665</v>
+        <v>3.470588235294118</v>
       </c>
       <c r="D12" t="n">
         <v>1.5</v>
@@ -1165,69 +1168,69 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>neo_limpo</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>ProjectMedian</t>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.61731843575419</v>
+        <v>3.51929737991607</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.866551518440247</v>
       </c>
       <c r="E13" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.599162011173184</v>
+        <v>3.554864253393665</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E14" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>ZS1</t>
+          <t>média(PM×tipo, SVR texto+meta)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.664804469273743</v>
+        <v>3.376406464024076</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1.665561454707328</v>
       </c>
       <c r="E15" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP do projeto</t>
+          <t>ProjectMedian</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.681564245810056</v>
+        <v>1.61731843575419</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -1240,11 +1243,11 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP por tipo</t>
+          <t>ProjectMedian×tipo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.628491620111732</v>
+        <v>1.599162011173184</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -1257,14 +1260,14 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, parecidos</t>
+          <t>ZS1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.07122905027933</v>
+        <v>6.664804469273743</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>716</v>
@@ -1274,14 +1277,14 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>XGBoost (texto)</t>
+          <t>ZS1 + dist. SP do projeto</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.663149115093594</v>
+        <v>1.681564245810056</v>
       </c>
       <c r="D19" t="n">
-        <v>1.003653049468994</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>716</v>
@@ -1291,14 +1294,14 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>XGBoost texto+meta</t>
+          <t>ZS1 + dist. SP por tipo</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.553436543355441</v>
+        <v>1.628491620111732</v>
       </c>
       <c r="D20" t="n">
-        <v>0.934131920337677</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>716</v>
@@ -1308,11 +1311,11 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, FS parecidos)</t>
+          <t>FS mesmo projeto, parecidos</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.67108938547486</v>
+        <v>2.07122905027933</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -1325,14 +1328,14 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, XGBoost texto+meta)</t>
+          <t>XGBoost (texto)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.511439949940037</v>
+        <v>1.663149115093594</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9279715418815613</v>
+        <v>1.003653049468994</v>
       </c>
       <c r="E22" t="n">
         <v>716</v>
@@ -1342,23 +1345,125 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+          <t>XGBoost texto+meta</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.605446927374302</v>
+        <v>1.553436543355441</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0.934131920337677</v>
       </c>
       <c r="E23" t="n">
         <v>716</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>SVR (texto)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.601720318053583</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9004870910512414</v>
+      </c>
+      <c r="E24" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>SVR texto+meta</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.448431472568515</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7563734312152055</v>
+      </c>
+      <c r="E25" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.67108938547486</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.511439949940037</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9279715418815613</v>
+      </c>
+      <c r="E27" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.605446927374302</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, SVR texto+meta)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.474428124268125</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7857466847606687</v>
+      </c>
+      <c r="E29" t="n">
+        <v>716</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="A16:A29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1370,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1478,7 +1583,7 @@
         <v>884</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004123135289492568</v>
+        <v>0.005301173943633302</v>
       </c>
     </row>
     <row r="3">
@@ -1520,140 +1625,140 @@
         <v>884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02380488727776</v>
+        <v>0.03173984970368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP do projeto × PM×tipo</t>
+          <t>XGBoost do artigo: + metadados</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>XGBoost (texto)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP do projeto</t>
+          <t>XGBoost texto+meta</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.585972850678733</v>
+        <v>4.180030888696601</v>
       </c>
       <c r="F4" t="n">
-        <v>4.127828054298643</v>
+        <v>3.749579360447318</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5418552036199095</v>
+        <v>-0.4304515282492832</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2827912895927602</v>
+        <v>-0.703960811464765</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8167562217194568</v>
+        <v>-0.1778061364840599</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001039271925614601</v>
+        <v>2.197536305955648e-09</v>
       </c>
       <c r="K4" t="n">
         <v>884</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009353447330531405</v>
+        <v>2.856797197742343e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP por tipo × PM×tipo</t>
+          <t>SVR do artigo: + metadados</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>SVR (texto)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP por tipo</t>
+          <t>SVR texto+meta</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.585972850678733</v>
+        <v>3.806327292442361</v>
       </c>
       <c r="F5" t="n">
-        <v>3.668552036199095</v>
+        <v>3.309497062222206</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08257918552036199</v>
+        <v>-0.4968302302201542</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1979638009049774</v>
+        <v>-0.7120896743491957</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3529553167420812</v>
+        <v>-0.2971908554885169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3850837522493387</v>
+        <v>4.070594458408658e-11</v>
       </c>
       <c r="K5" t="n">
         <v>884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7701675044986773</v>
+        <v>6.105891687612988e-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, parecidos × PM×tipo</t>
+          <t>LLM do artigo: + SP do time por tipo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>ZS1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, parecidos</t>
+          <t>ZS1 + dist. SP por tipo</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.585972850678733</v>
+        <v>7.303167420814479</v>
       </c>
       <c r="F6" t="n">
-        <v>3.900452488687783</v>
+        <v>3.668552036199095</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3144796380090498</v>
+        <v>-3.634615384615385</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08945135746606332</v>
+        <v>-4.08939479638009</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7064621040723981</v>
+        <v>-3.171945701357466</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08366444217402481</v>
+        <v>1.630566486302048e-62</v>
       </c>
       <c r="K6" t="n">
         <v>884</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4183222108701241</v>
+        <v>2.608906378083277e-61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>XGBoost (texto) × PM×tipo</t>
+          <t>ZS1 + dist. SP do projeto × PM×tipo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1663,39 +1768,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XGBoost (texto)</t>
+          <t>ZS1 + dist. SP do projeto</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>3.585972850678733</v>
       </c>
       <c r="F7" t="n">
-        <v>4.180030888696601</v>
+        <v>4.127828054298643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5940580380178685</v>
+        <v>0.5418552036199095</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3447557966734759</v>
+        <v>0.2827912895927602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8562664493547572</v>
+        <v>0.8167562217194568</v>
       </c>
       <c r="J7" t="n">
-        <v>5.80994720219041e-11</v>
+        <v>0.0001039271925614601</v>
       </c>
       <c r="K7" t="n">
         <v>884</v>
       </c>
       <c r="L7" t="n">
-        <v>5.809947202190411e-10</v>
+        <v>0.001143199118176061</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>XGBoost texto+meta × PM×tipo</t>
+          <t>ZS1 + dist. SP por tipo × PM×tipo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1705,39 +1810,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XGBoost texto+meta</t>
+          <t>ZS1 + dist. SP por tipo</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>3.585972850678733</v>
       </c>
       <c r="F8" t="n">
-        <v>3.749579360447318</v>
+        <v>3.668552036199095</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1636065097685853</v>
+        <v>0.08257918552036199</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.08538474067371353</v>
+        <v>-0.1979638009049774</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4281635838564975</v>
+        <v>0.3529553167420812</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003919915650195702</v>
+        <v>0.3850837522493387</v>
       </c>
       <c r="K8" t="n">
         <v>884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003135932520156562</v>
+        <v>0.7701675044986773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, FS parecidos) × PM×tipo</t>
+          <t>FS mesmo projeto, parecidos × PM×tipo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1747,26 +1852,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>média(PM×tipo, FS parecidos)</t>
+          <t>FS mesmo projeto, parecidos</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>3.585972850678733</v>
       </c>
       <c r="F9" t="n">
-        <v>3.470588235294118</v>
+        <v>3.900452488687783</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1153846153846154</v>
+        <v>0.3144796380090498</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3308823529411765</v>
+        <v>-0.08945135746606332</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09220871040723962</v>
+        <v>0.7064621040723981</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09363356319641962</v>
+        <v>0.08366444217402481</v>
       </c>
       <c r="K9" t="n">
         <v>884</v>
@@ -1779,7 +1884,7 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, XGBoost texto+meta) × PM×tipo</t>
+          <t>XGBoost (texto) × PM×tipo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1789,39 +1894,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>média(PM×tipo, XGBoost texto+meta)</t>
+          <t>XGBoost (texto)</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>3.585972850678733</v>
       </c>
       <c r="F10" t="n">
-        <v>3.51929737991607</v>
+        <v>4.180030888696601</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06667547076266275</v>
+        <v>0.5940580380178685</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2071099228937836</v>
+        <v>0.3447557966734759</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0769335954471141</v>
+        <v>0.8562664493547572</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2374570013530297</v>
+        <v>5.80994720219041e-11</v>
       </c>
       <c r="K10" t="n">
         <v>884</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7123710040590892</v>
+        <v>8.133926083066574e-10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, ZS1 + dist. SP por tipo) × PM×tipo</t>
+          <t>XGBoost texto+meta × PM×tipo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1831,127 +1936,123 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+          <t>XGBoost texto+meta</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3.585972850678733</v>
       </c>
       <c r="F11" t="n">
-        <v>3.554864253393665</v>
+        <v>3.749579360447318</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03110859728506787</v>
+        <v>0.1636065097685853</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1792986425339367</v>
+        <v>-0.08538474067371353</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1088871606334841</v>
+        <v>0.4281635838564975</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8824667925909202</v>
+        <v>0.0003919915650195702</v>
       </c>
       <c r="K11" t="n">
         <v>884</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8824667925909202</v>
+        <v>0.003919915650195702</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>neo_limpo</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>tipo na mediana</t>
+          <t>SVR (texto) × PM×tipo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ProjectMedian</t>
+          <t>ProjectMedian×tipo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>SVR (texto)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.61731843575419</v>
+        <v>3.585972850678733</v>
       </c>
       <c r="F12" t="n">
-        <v>1.599162011173184</v>
+        <v>3.806327292442361</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01815642458100559</v>
+        <v>0.2203544417636276</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.05935754189944134</v>
+        <v>-0.001566747758942738</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02583798882681564</v>
+        <v>0.4489188694161866</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1478497680634144</v>
+        <v>0.005680129170329669</v>
       </c>
       <c r="K12" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7392488403170718</v>
+        <v>0.03976090419230768</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>LLM: dist. por tipo × do projeto</t>
+          <t>SVR texto+meta × PM×tipo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP do projeto</t>
+          <t>ProjectMedian×tipo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP por tipo</t>
+          <t>SVR texto+meta</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.681564245810056</v>
+        <v>3.585972850678733</v>
       </c>
       <c r="F13" t="n">
-        <v>1.628491620111732</v>
+        <v>3.309497062222206</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.05307262569832402</v>
+        <v>-0.2764757884565265</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.11875</v>
+        <v>-0.4407963412618484</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01675977653631285</v>
+        <v>-0.1189512506785605</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1211923456636531</v>
+        <v>0.009549246215475487</v>
       </c>
       <c r="K13" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7271540739819184</v>
+        <v>0.05729547729285292</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP do projeto × PM×tipo</t>
+          <t>média(PM×tipo, FS parecidos) × PM×tipo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1961,39 +2062,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP do projeto</t>
+          <t>média(PM×tipo, FS parecidos)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.599162011173184</v>
+        <v>3.585972850678733</v>
       </c>
       <c r="F14" t="n">
-        <v>1.681564245810056</v>
+        <v>3.470588235294118</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0824022346368715</v>
+        <v>-0.1153846153846154</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01256983240223464</v>
+        <v>-0.3308823529411765</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1536312849162011</v>
+        <v>0.09220871040723962</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007113810551882393</v>
+        <v>0.09363356319641962</v>
       </c>
       <c r="K14" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05691048441505914</v>
+        <v>0.4183222108701241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP por tipo × PM×tipo</t>
+          <t>média(PM×tipo, XGBoost texto+meta) × PM×tipo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2003,39 +2104,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ZS1 + dist. SP por tipo</t>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.599162011173184</v>
+        <v>3.585972850678733</v>
       </c>
       <c r="F15" t="n">
-        <v>1.628491620111732</v>
+        <v>3.51929737991607</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02932960893854749</v>
+        <v>-0.06667547076266275</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.04399441340782123</v>
+        <v>-0.2071099228937836</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09986033519553073</v>
+        <v>0.0769335954471141</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1489722858537362</v>
+        <v>0.2374570013530297</v>
       </c>
       <c r="K15" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7392488403170718</v>
+        <v>0.7123710040590892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, parecidos × PM×tipo</t>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo) × PM×tipo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2045,39 +2146,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FS mesmo projeto, parecidos</t>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.599162011173184</v>
+        <v>3.585972850678733</v>
       </c>
       <c r="F16" t="n">
-        <v>2.07122905027933</v>
+        <v>3.554864253393665</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4720670391061452</v>
+        <v>-0.03110859728506787</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2401885474860335</v>
+        <v>-0.1792986425339367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6864525139664804</v>
+        <v>0.1088871606334841</v>
       </c>
       <c r="J16" t="n">
-        <v>9.644777585034093e-12</v>
+        <v>0.8824667925909202</v>
       </c>
       <c r="K16" t="n">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="L16" t="n">
-        <v>9.644777585034092e-11</v>
+        <v>0.8824667925909202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>XGBoost (texto) × PM×tipo</t>
+          <t>média(PM×tipo, SVR texto+meta) × PM×tipo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2087,206 +2188,714 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>XGBoost (texto)</t>
+          <t>média(PM×tipo, SVR texto+meta)</t>
         </is>
       </c>
       <c r="E17" t="n">
+        <v>3.585972850678733</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.376406464024076</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2095663866546568</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2938164642094615</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.1265014773202487</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.510761768791646e-05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>884</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0001812914122549976</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>tipo na mediana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ProjectMedian</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.61731843575419</v>
+      </c>
+      <c r="F18" t="n">
         <v>1.599162011173184</v>
       </c>
-      <c r="F17" t="n">
-        <v>1.663149115093594</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.06398710392040914</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.2308945169870081</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.2944828639524941</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.004060825233422018</v>
-      </c>
-      <c r="K17" t="n">
-        <v>716</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.03654742710079817</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost texto+meta × PM×tipo</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ProjectMedian×tipo</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>XGBoost texto+meta</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.599162011173184</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.553436543355441</v>
-      </c>
       <c r="G18" t="n">
-        <v>-0.0457254678177434</v>
+        <v>-0.01815642458100559</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3088484352194397</v>
+        <v>-0.05935754189944134</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1397534304366098</v>
+        <v>0.02583798882681564</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1886294022110985</v>
+        <v>0.1478497680634144</v>
       </c>
       <c r="K18" t="n">
         <v>716</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7392488403170718</v>
+        <v>0.8870986083804863</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, FS parecidos) × PM×tipo</t>
+          <t>LLM: dist. por tipo × do projeto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>ZS1 + dist. SP do projeto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>média(PM×tipo, FS parecidos)</t>
+          <t>ZS1 + dist. SP por tipo</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.599162011173184</v>
+        <v>1.681564245810056</v>
       </c>
       <c r="F19" t="n">
-        <v>1.67108938547486</v>
+        <v>1.628491620111732</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07192737430167598</v>
+        <v>-0.05307262569832402</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.05028805865921788</v>
+        <v>-0.11875</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1854137569832401</v>
+        <v>0.01675977653631285</v>
       </c>
       <c r="J19" t="n">
-        <v>0.009737844673201594</v>
+        <v>0.1211923456636531</v>
       </c>
       <c r="K19" t="n">
         <v>716</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06816491271241115</v>
+        <v>0.8483464196455716</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, XGBoost texto+meta) × PM×tipo</t>
+          <t>XGBoost do artigo: + metadados</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>XGBoost (texto)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>média(PM×tipo, XGBoost texto+meta)</t>
+          <t>XGBoost texto+meta</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.599162011173184</v>
+        <v>1.663149115093594</v>
       </c>
       <c r="F20" t="n">
-        <v>1.511439949940037</v>
+        <v>1.553436543355441</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.08772206123314756</v>
+        <v>-0.1097125717381525</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2251296382168485</v>
+        <v>-0.2104072729177648</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0155138952480681</v>
+        <v>-0.03485230301095794</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8771992486932699</v>
+        <v>0.001538315008385665</v>
       </c>
       <c r="K20" t="n">
         <v>716</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8771992486932699</v>
+        <v>0.01845978010062798</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>média(PM×tipo, ZS1 + dist. SP por tipo) × PM×tipo</t>
+          <t>SVR do artigo: + metadados</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ProjectMedian×tipo</t>
+          <t>SVR (texto)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+          <t>SVR texto+meta</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.599162011173184</v>
+        <v>1.601720318053583</v>
       </c>
       <c r="F21" t="n">
-        <v>1.605446927374302</v>
+        <v>1.448431472568515</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006284916201117319</v>
+        <v>-0.1532888454850677</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.03002793296089385</v>
+        <v>-0.2117464680779499</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04259776536312849</v>
+        <v>-0.09375461554192456</v>
       </c>
       <c r="J21" t="n">
-        <v>0.286891627053746</v>
+        <v>4.656727175394342e-08</v>
       </c>
       <c r="K21" t="n">
         <v>716</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7392488403170718</v>
+        <v>6.519418045552079e-07</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>LLM do artigo: + SP do time por tipo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ZS1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6.664804469273743</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.628491620111732</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-5.036312849162011</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-5.332402234636872</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-4.731843575418995</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.585482754797062e-94</v>
+      </c>
+      <c r="K22" t="n">
+        <v>716</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4.136772407675299e-93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP do projeto</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.681564245810056</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0824022346368715</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01256983240223464</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1536312849162011</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.007113810551882393</v>
+      </c>
+      <c r="K23" t="n">
+        <v>716</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.07113810551882394</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ZS1 + dist. SP por tipo</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.628491620111732</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.02932960893854749</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.04399441340782123</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09986033519553073</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1489722858537362</v>
+      </c>
+      <c r="K24" t="n">
+        <v>716</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.8870986083804863</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FS mesmo projeto, parecidos</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.07122905027933</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4720670391061452</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2401885474860335</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6864525139664804</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9.644777585034093e-12</v>
+      </c>
+      <c r="K25" t="n">
+        <v>716</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.446716637755114e-10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost (texto) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>XGBoost (texto)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.663149115093594</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.06398710392040914</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2308945169870081</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2944828639524941</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.004060825233422018</v>
+      </c>
+      <c r="K26" t="n">
+        <v>716</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0446690775676422</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>XGBoost texto+meta</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.553436543355441</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.0457254678177434</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.3088484352194397</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1397534304366098</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.1886294022110985</v>
+      </c>
+      <c r="K27" t="n">
+        <v>716</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.8870986083804863</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>SVR (texto) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SVR (texto)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.601720318053583</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.002558306880398251</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.08635640426243003</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0865833418302492</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1661641551486346</v>
+      </c>
+      <c r="K28" t="n">
+        <v>716</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.8870986083804863</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>SVR texto+meta × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SVR texto+meta</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.448431472568515</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.1507305386046695</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.2361470632965425</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.06663147795654431</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.01842753234769029</v>
+      </c>
+      <c r="K29" t="n">
+        <v>716</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1474202587815223</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, FS parecidos)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.67108938547486</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.07192737430167598</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.05028805865921788</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1854137569832401</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.009737844673201594</v>
+      </c>
+      <c r="K30" t="n">
+        <v>716</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.08764060205881435</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, XGBoost texto+meta)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.511439949940037</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.08772206123314756</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.2251296382168485</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.0155138952480681</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8771992486932699</v>
+      </c>
+      <c r="K31" t="n">
+        <v>716</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.8870986083804863</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, ZS1 + dist. SP por tipo)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.605446927374302</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.006284916201117319</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.03002793296089385</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.04259776536312849</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.286891627053746</v>
+      </c>
+      <c r="K32" t="n">
+        <v>716</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.8870986083804863</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, SVR texto+meta) × PM×tipo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ProjectMedian×tipo</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>média(PM×tipo, SVR texto+meta)</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1.599162011173184</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.474428124268125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.1247338869050596</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.1707571047471957</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.08107522419080927</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.325757434836826e-05</v>
+      </c>
+      <c r="K33" t="n">
+        <v>716</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0004323484665287874</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A18:A33"/>
+    <mergeCell ref="A2:A17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8721,6 +9330,2498 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reescritas</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>similaridade_mediana</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>frases_sustentadas_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>com_contradicao_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>entidades_preservadas_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>com_entidade_inventada_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>suspeitas_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>parafrasear</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>143</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>79</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>parafrasear</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>161</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>160</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>melhorar_contexto</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>53</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>53</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>issue_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>motivo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ent_inventadas</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>frases_nao_sustentadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>870</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>USERGRID-00137</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>entidade inventada</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>To resolve the 500 error returned with a high load of PUT operations and ensure that the 'version is required to be set for an update operation' error message is handled correctly. || Update the PUT operation to require a valid version for update operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>755</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MDL-00069</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>67% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>To provide a consistent user experience by restoring the checkbox option for sending feedback after grading an assignment || Restore the checkbox option for sending feedback after grading an assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>760</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MDL-00675</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>67% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Compile LESS from PHP. || Moodle UI, PHP, LESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>764</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MDL-00957</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>100% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>To investigate why the data-target property is not functioning as expected and resolve the issue. || Analyze the current implementation of the data-target property and identify the root cause of the problem. || Moodle's theme components, specifically those based on Bootstrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>768</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MESOS-01026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Test case(s) for weights + allocation behavior. || To create test cases for the behavior when weights are defined, ensuring the correct allocation and usage of resources. || Create test cases for the weights and allocation behavior, possibly including subtasks such as identifying the current lack of test cases and designing the new test cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>769</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MESOS-01068</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flaky test needs to be fixed to ensure reliable testing || leveldb.cpp, replica.cpp, recover.cpp, master.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>770</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MESOS-01228</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>To investigate and resolve the flakiness of ROOT_DOCKER_Logs. || To analyze the logs and identify the root cause of the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>772</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MESOS-01587</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>67% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>To identify and resolve the issue causing the master to crash when performing the UNRESERVE operation. || Investigate and fix the root cause of the master failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>776</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MULE-00204</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>80% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>To resolve the issue with the Streaming feature not working with large queries and provide a meaningful error message. || Subtasks: Determine the root cause of the issue, identify the problematic queries, and implement a solution to handle them. || Mule flow, database module, Streaming feature || Error message is displayed when an issue occurs, and results are returned for small queries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>779</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MULE-00348</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>75% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fix DatabaseMuleArtifactTestCase after Maven changes to ensure it runs correctly. || Revert changes to DatabaseMuleArtifactTestCase to make it compatible with new Maven configuration. || DatabaseMuleArtifactTestCase runs without errors after Maven changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>789</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TIMOB-02109</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>60% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>To resolve the compilation error on iOS without changing any code, ensuring the app can be compiled again. || Identify and fix the compilation error without modifying the code. || The app can be compiled without errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>794</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USERGRID-00144</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>57% das frases não sustentadas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Resolve NullPointerException when updating an entity without setting the version || ['Check if the version is set before calling the update method', 'Verify that the update method checks for a null version'] || ['Other teams', 'Third-party services', 'Hardware or upstream issues'] || ['The update operation should not throw a NullPointerException when the version is set', 'The update method should check for a null version and throw an exception if it is null']</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Δ MAE (B − A)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IC95% inf</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IC95% sup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>só fiéis</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>só fiéis</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>só fiéis</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>todas</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>só fiéis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>estimador</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>contraste</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>LLM por analogia (2g)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.582</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.543</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.686</v>
+      </c>
+      <c r="J4" t="n">
+        <v>79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto × controle</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.278</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3.545</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>79</v>
+      </c>
+      <c r="K5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.911</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.785</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>79</v>
+      </c>
+      <c r="K6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>melhorar com contexto</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.057</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.114</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>79</v>
+      </c>
+      <c r="K7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>melhorar com contexto × controle</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.646</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-2.038</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.229</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="J8" t="n">
+        <v>79</v>
+      </c>
+      <c r="K8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>melhorar × controle</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.747</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.629</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>79</v>
+      </c>
+      <c r="K9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.937</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.971</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.514</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.856999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>79</v>
+      </c>
+      <c r="K10" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.061</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.352</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.136</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.834</v>
+      </c>
+      <c r="J11" t="n">
+        <v>132</v>
+      </c>
+      <c r="K11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto × controle</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.462</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.574</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.849</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.759</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="J12" t="n">
+        <v>132</v>
+      </c>
+      <c r="K12" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.074</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.182</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.259</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.889</v>
+      </c>
+      <c r="J13" t="n">
+        <v>132</v>
+      </c>
+      <c r="K13" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>melhorar com contexto</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.704</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.637</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.426</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.259</v>
+      </c>
+      <c r="J14" t="n">
+        <v>132</v>
+      </c>
+      <c r="K14" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>melhorar com contexto × controle</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.152</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.038</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.759</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="J15" t="n">
+        <v>132</v>
+      </c>
+      <c r="K15" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>melhorar × controle</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.356</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="J16" t="n">
+        <v>132</v>
+      </c>
+      <c r="K16" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.432</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.759</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.537</v>
+      </c>
+      <c r="J17" t="n">
+        <v>132</v>
+      </c>
+      <c r="K17" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.842</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.868</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.684</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>53</v>
+      </c>
+      <c r="K18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>estruturar_contexto × controle</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.421</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="J19" t="n">
+        <v>53</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>melhorar</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.377</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.368</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.264</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.738</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="J20" t="n">
+        <v>53</v>
+      </c>
+      <c r="K20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>melhorar com contexto</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.302</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.789</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.981</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.842</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="J21" t="n">
+        <v>53</v>
+      </c>
+      <c r="K21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>melhorar com contexto × controle</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.263</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="J22" t="n">
+        <v>53</v>
+      </c>
+      <c r="K22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>melhorar × controle</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.264</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="J23" t="n">
+        <v>53</v>
+      </c>
+      <c r="K23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.887</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.053</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.604</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.842</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.208</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.368</v>
+      </c>
+      <c r="J24" t="n">
+        <v>53</v>
+      </c>
+      <c r="K24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>LLM zero-shot (fatorial)</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>agile_limpo</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre (mesma informação)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.101</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.571</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.861</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.714</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="J25" t="n">
+        <v>79</v>
+      </c>
+      <c r="K25" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.229</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.924</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.371</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>79</v>
+      </c>
+      <c r="K26" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>estruturada, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.734</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="J27" t="n">
+        <v>79</v>
+      </c>
+      <c r="K27" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>reescrita estruturada com contexto</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.143</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="J28" t="n">
+        <v>79</v>
+      </c>
+      <c r="K28" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre com contexto</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.371</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.747</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="J29" t="n">
+        <v>79</v>
+      </c>
+      <c r="K29" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre, sem contexto</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.229</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.873</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>79</v>
+      </c>
+      <c r="K30" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.144</v>
+      </c>
+      <c r="J31" t="n">
+        <v>79</v>
+      </c>
+      <c r="K31" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>só o contexto no estimador</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.714</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-1.743</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.392</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="J32" t="n">
+        <v>79</v>
+      </c>
+      <c r="K32" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (estruturada)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.371</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="J33" t="n">
+        <v>79</v>
+      </c>
+      <c r="K33" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (livre)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.342</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.286</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="J34" t="n">
+        <v>79</v>
+      </c>
+      <c r="K34" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre (mesma informação)</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-1.129</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1.704</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-2.574</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.523</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.833</v>
+      </c>
+      <c r="J35" t="n">
+        <v>132</v>
+      </c>
+      <c r="K35" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.455</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.352</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.985</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1.259</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="J36" t="n">
+        <v>132</v>
+      </c>
+      <c r="K36" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>estruturada, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="J37" t="n">
+        <v>132</v>
+      </c>
+      <c r="K37" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>reescrita estruturada com contexto</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.204</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-1.019</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="J38" t="n">
+        <v>132</v>
+      </c>
+      <c r="K38" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre com contexto</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.204</v>
+      </c>
+      <c r="J39" t="n">
+        <v>132</v>
+      </c>
+      <c r="K39" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre, sem contexto</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="J40" t="n">
+        <v>132</v>
+      </c>
+      <c r="K40" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="J41" t="n">
+        <v>132</v>
+      </c>
+      <c r="K41" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>só o contexto no estimador</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.8149999999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-1.685</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.5610000000000001</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J42" t="n">
+        <v>132</v>
+      </c>
+      <c r="K42" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (estruturada)</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.402</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.648</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="J43" t="n">
+        <v>132</v>
+      </c>
+      <c r="K43" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (livre)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="J44" t="n">
+        <v>132</v>
+      </c>
+      <c r="K44" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>neo_limpo</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre (mesma informação)</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-1.947</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-2.113</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-3.158</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.226</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.737</v>
+      </c>
+      <c r="J45" t="n">
+        <v>53</v>
+      </c>
+      <c r="K45" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>estruturada × livre, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.736</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.579</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.585</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-2.053</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="J46" t="n">
+        <v>53</v>
+      </c>
+      <c r="K46" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>estruturada, com cartão no estimador</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1.226</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-1.158</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="J47" t="n">
+        <v>53</v>
+      </c>
+      <c r="K47" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="n"/>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>reescrita estruturada com contexto</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.211</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.5659999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-1.789</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="J48" t="n">
+        <v>53</v>
+      </c>
+      <c r="K48" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre com contexto</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.895</v>
+      </c>
+      <c r="J49" t="n">
+        <v>53</v>
+      </c>
+      <c r="K49" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="1" t="n"/>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>reescrita livre, sem contexto</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="J50" t="n">
+        <v>53</v>
+      </c>
+      <c r="K50" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>só mexer no texto (controle)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.842</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="J51" t="n">
+        <v>53</v>
+      </c>
+      <c r="K51" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="n"/>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>só o contexto no estimador</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-1.057</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1.774</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-2.579</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.321</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="J52" t="n">
+        <v>53</v>
+      </c>
+      <c r="K52" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="1" t="n"/>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (estruturada)</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.316</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-2.107</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="J53" t="n">
+        <v>53</v>
+      </c>
+      <c r="K53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="n"/>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>tudo junto (livre)</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-1.368</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.842</v>
+      </c>
+      <c r="J54" t="n">
+        <v>53</v>
+      </c>
+      <c r="K54" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A4:A24"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B18:B24"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="A25:A54"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="B35:B44"/>
+    <mergeCell ref="B11:B17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
